--- a/tenant_application_forms/036_tenant_digital_portal_pilot_application_form--tenant_application_forms.xlsx
+++ b/tenant_application_forms/036_tenant_digital_portal_pilot_application_form--tenant_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'applied'}</t>
+          <t>applied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'applied'}</t>
+          <t>applied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'leased'}</t>
+          <t>leased</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'leased'}</t>
+          <t>leased</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'not_leased'}</t>
+          <t>not_leased</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'not_leased'}</t>
+          <t>not leased</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'house'}</t>
+          <t>house</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'house'}</t>
+          <t>house</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'apartment'}</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'apartment'}</t>
+          <t>apartment</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'reported_area_size_1_sq_ft',_'label':_'reported_area_size_1_sq_ft'}</t>
+          <t>reported_area_size_1_sq_ft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'reported_area_size_1_sq_ft', 'label': 'Reported Area Size 1 Sq Ft'}</t>
+          <t>Reported Area Size 1 Sq Ft</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'reported_area_size_2_sq_in',_'label':_'reported_area_size_2_sq_in'}</t>
+          <t>reported_area_size_2_sq_in</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'reported_area_size_2_sq_in', 'label': 'Reported Area Size 2 Sq In'}</t>
+          <t>Reported Area Size 2 Sq In</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'reported_area_size_3_sq_m',_'label':_'reported_area_size_3_sq_m'}</t>
+          <t>reported_area_size_3_sq_m</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'reported_area_size_3_sq_m', 'label': 'Reported Area Size 3 Sq M'}</t>
+          <t>Reported Area Size 3 Sq M</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'lease'}</t>
+          <t>lease</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'lease'}</t>
+          <t>lease</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'sublease'}</t>
+          <t>sublease</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'sublease'}</t>
+          <t>sublease</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lease_status_choices</t>
+          <t>lease_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'sublease'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'sublease'}</t>
+          <t>single</t>
         </is>
       </c>
     </row>
@@ -1335,46 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'single'}</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'single'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>lease_type_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'value':_'joint'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'value': 'joint'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>lease_type_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'value':_'joint'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'value': 'joint'}</t>
+          <t>joint</t>
         </is>
       </c>
     </row>
